--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-03).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-03).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>R$ 9.914,58</t>
-  </si>
-  <si>
-    <t>102.2</t>
-  </si>
-  <si>
-    <t>66.9</t>
-  </si>
-  <si>
-    <t>6.21</t>
-  </si>
-  <si>
-    <t>21.1</t>
-  </si>
-  <si>
-    <t>8.1</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>32.1%</t>
-  </si>
-  <si>
-    <t>16.3%</t>
+    <t>37</t>
+  </si>
+  <si>
+    <t>R$ 9.633,55</t>
+  </si>
+  <si>
+    <t>99.2</t>
+  </si>
+  <si>
+    <t>64.9</t>
+  </si>
+  <si>
+    <t>6.50</t>
+  </si>
+  <si>
+    <t>22.1</t>
+  </si>
+  <si>
+    <t>8.9</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>31.3%</t>
+  </si>
+  <si>
+    <t>18.2%</t>
   </si>
   <si>
     <t>1.4%</t>
@@ -971,58 +971,58 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>2.6%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
+    <t>2.8%</t>
+  </si>
+  <si>
+    <t>0.9%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>4.5%</t>
+    <t>5.4%</t>
   </si>
   <si>
     <t>2.7%</t>
   </si>
   <si>
-    <t>6.0%</t>
-  </si>
-  <si>
-    <t>1741.0</t>
-  </si>
-  <si>
-    <t>1525.0</t>
-  </si>
-  <si>
-    <t>134.0</t>
-  </si>
-  <si>
-    <t>27.0</t>
-  </si>
-  <si>
-    <t>245.0</t>
-  </si>
-  <si>
-    <t>63.0</t>
-  </si>
-  <si>
-    <t>11.0</t>
-  </si>
-  <si>
-    <t>420.0</t>
-  </si>
-  <si>
-    <t>253.0</t>
-  </si>
-  <si>
-    <t>561.0</t>
+    <t>7.3%</t>
+  </si>
+  <si>
+    <t>2396.0</t>
+  </si>
+  <si>
+    <t>2062.0</t>
+  </si>
+  <si>
+    <t>159.0</t>
+  </si>
+  <si>
+    <t>37.0</t>
+  </si>
+  <si>
+    <t>314.0</t>
+  </si>
+  <si>
+    <t>98.0</t>
+  </si>
+  <si>
+    <t>14.0</t>
+  </si>
+  <si>
+    <t>610.0</t>
+  </si>
+  <si>
+    <t>307.0</t>
+  </si>
+  <si>
+    <t>823.0</t>
   </si>
   <si>
     <t>0.6%</t>
   </si>
   <si>
-    <t>54.0</t>
+    <t>71.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3242,7 +3242,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -3272,35 +3272,93 @@
         <v>58</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="M13" s="5">
+        <v>14289.639999999999</v>
+      </c>
+      <c r="N13" s="6">
+        <v>150</v>
+      </c>
+      <c r="O13" s="6">
+        <v>119</v>
+      </c>
+      <c r="P13" s="7">
+        <v>15.338709677419354</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>31.145237815126052</v>
+      </c>
+      <c r="R13" s="8">
+        <v>7.3942579831932775</v>
+      </c>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0.1092436974789916</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.033613445378151259</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.0084033613445378148</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>21</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>21</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>14</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0.01680672268907563</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -5316,7 +5374,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>51</v>
@@ -5346,35 +5404,93 @@
         <v>58</v>
       </c>
       <c r="L27" s="4"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
-      <c r="AD27" s="6"/>
-      <c r="AE27" s="6"/>
-      <c r="AF27" s="6"/>
-      <c r="AG27" s="6"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="6"/>
-      <c r="AJ27" s="6"/>
-      <c r="AK27" s="6"/>
-      <c r="AL27" s="6"/>
-      <c r="AM27" s="6"/>
-      <c r="AN27" s="9"/>
-      <c r="AO27" s="6"/>
+      <c r="M27" s="5">
+        <v>7991.9099999999999</v>
+      </c>
+      <c r="N27" s="6">
+        <v>74</v>
+      </c>
+      <c r="O27" s="6">
+        <v>45</v>
+      </c>
+      <c r="P27" s="7">
+        <v>4.2509528571428579</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>20.585926666666669</v>
+      </c>
+      <c r="R27" s="8">
+        <v>8.4514822222222232</v>
+      </c>
+      <c r="S27" s="8">
+        <v>8</v>
+      </c>
+      <c r="T27" s="9">
+        <v>0.28888888888888886</v>
+      </c>
+      <c r="U27" s="9">
+        <v>0.17777777777777778</v>
+      </c>
+      <c r="V27" s="9">
+        <v>0.044444444444444446</v>
+      </c>
+      <c r="W27" s="9">
+        <v>0</v>
+      </c>
+      <c r="X27" s="9">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="Y27" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="9">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="AB27" s="9">
+        <v>0.088888888888888892</v>
+      </c>
+      <c r="AC27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF27" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL27" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP27" s="4">
         <v>58</v>
       </c>
@@ -5671,7 +5787,7 @@
         <v>19550</v>
       </c>
       <c r="B30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C30" s="4">
         <v>51</v>
@@ -5701,35 +5817,93 @@
         <v>58</v>
       </c>
       <c r="L30" s="4"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="8"/>
-      <c r="R30" s="8"/>
-      <c r="S30" s="8"/>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="9"/>
-      <c r="Z30" s="9"/>
-      <c r="AA30" s="9"/>
-      <c r="AB30" s="9"/>
-      <c r="AC30" s="9"/>
-      <c r="AD30" s="6"/>
-      <c r="AE30" s="6"/>
-      <c r="AF30" s="6"/>
-      <c r="AG30" s="6"/>
-      <c r="AH30" s="6"/>
-      <c r="AI30" s="6"/>
-      <c r="AJ30" s="6"/>
-      <c r="AK30" s="6"/>
-      <c r="AL30" s="6"/>
-      <c r="AM30" s="6"/>
-      <c r="AN30" s="9"/>
-      <c r="AO30" s="6"/>
+      <c r="M30" s="5">
+        <v>11029.75</v>
+      </c>
+      <c r="N30" s="6">
+        <v>94</v>
+      </c>
+      <c r="O30" s="6">
+        <v>31</v>
+      </c>
+      <c r="P30" s="7">
+        <v>8.9524819148936174</v>
+      </c>
+      <c r="Q30" s="8">
+        <v>34.199461290322581</v>
+      </c>
+      <c r="R30" s="8">
+        <v>17.520967741935483</v>
+      </c>
+      <c r="S30" s="8">
+        <v>7</v>
+      </c>
+      <c r="T30" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="U30" s="9">
+        <v>0.29032258064516131</v>
+      </c>
+      <c r="V30" s="9">
+        <v>0.29032258064516131</v>
+      </c>
+      <c r="W30" s="9">
+        <v>0</v>
+      </c>
+      <c r="X30" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE30" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF30" s="6">
+        <v>9</v>
+      </c>
+      <c r="AG30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP30" s="4">
         <v>58</v>
       </c>
@@ -6906,7 +7080,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -6936,35 +7110,93 @@
         <v>58</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="9"/>
-      <c r="AO39" s="6"/>
+      <c r="M39" s="5">
+        <v>10373.17</v>
+      </c>
+      <c r="N39" s="6">
+        <v>117</v>
+      </c>
+      <c r="O39" s="6">
+        <v>72</v>
+      </c>
+      <c r="P39" s="7">
+        <v>2.3862321739130432</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>18.721295833333333</v>
+      </c>
+      <c r="R39" s="8">
+        <v>8.7480681159420293</v>
+      </c>
+      <c r="S39" s="8">
+        <v>8</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="U39" s="9">
+        <v>0.18055555555555555</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.069444444444444448</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.069444444444444448</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
       </c>
@@ -7575,7 +7807,7 @@
         <v>19581</v>
       </c>
       <c r="B44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C44" s="4">
         <v>51</v>
@@ -7605,35 +7837,93 @@
         <v>58</v>
       </c>
       <c r="L44" s="4"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="6"/>
-      <c r="P44" s="7"/>
-      <c r="Q44" s="8"/>
-      <c r="R44" s="8"/>
-      <c r="S44" s="8"/>
-      <c r="T44" s="9"/>
-      <c r="U44" s="9"/>
-      <c r="V44" s="9"/>
-      <c r="W44" s="9"/>
-      <c r="X44" s="9"/>
-      <c r="Y44" s="9"/>
-      <c r="Z44" s="9"/>
-      <c r="AA44" s="9"/>
-      <c r="AB44" s="9"/>
-      <c r="AC44" s="9"/>
-      <c r="AD44" s="6"/>
-      <c r="AE44" s="6"/>
-      <c r="AF44" s="6"/>
-      <c r="AG44" s="6"/>
-      <c r="AH44" s="6"/>
-      <c r="AI44" s="6"/>
-      <c r="AJ44" s="6"/>
-      <c r="AK44" s="6"/>
-      <c r="AL44" s="6"/>
-      <c r="AM44" s="6"/>
-      <c r="AN44" s="9"/>
-      <c r="AO44" s="6"/>
+      <c r="M44" s="5">
+        <v>13808.049999999999</v>
+      </c>
+      <c r="N44" s="6">
+        <v>130</v>
+      </c>
+      <c r="O44" s="6">
+        <v>116</v>
+      </c>
+      <c r="P44" s="7">
+        <v>5.0192984962406015</v>
+      </c>
+      <c r="Q44" s="8">
+        <v>19.066092241379312</v>
+      </c>
+      <c r="R44" s="8">
+        <v>7.3683168316831686</v>
+      </c>
+      <c r="S44" s="8">
+        <v>8</v>
+      </c>
+      <c r="T44" s="9">
+        <v>0.31034482758620691</v>
+      </c>
+      <c r="U44" s="9">
+        <v>0.27586206896551724</v>
+      </c>
+      <c r="V44" s="9">
+        <v>0</v>
+      </c>
+      <c r="W44" s="9">
+        <v>0.017241379309999999</v>
+      </c>
+      <c r="X44" s="9">
+        <v>0.043103448275862072</v>
+      </c>
+      <c r="Y44" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="9">
+        <v>0.16379310344827586</v>
+      </c>
+      <c r="AB44" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="9">
+        <v>0.051724137931034482</v>
+      </c>
+      <c r="AD44" s="6">
+        <v>30</v>
+      </c>
+      <c r="AE44" s="6">
+        <v>32</v>
+      </c>
+      <c r="AF44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="6">
+        <v>2</v>
+      </c>
+      <c r="AH44" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="6">
+        <v>19</v>
+      </c>
+      <c r="AL44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN44" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO44" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP44" s="4">
         <v>58</v>
       </c>
@@ -9178,7 +9468,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -9208,35 +9498,93 @@
         <v>58</v>
       </c>
       <c r="L55" s="4"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="8"/>
-      <c r="S55" s="8"/>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
-      <c r="W55" s="9"/>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
-      <c r="AC55" s="9"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="6"/>
-      <c r="AL55" s="6"/>
-      <c r="AM55" s="6"/>
-      <c r="AN55" s="9"/>
-      <c r="AO55" s="6"/>
+      <c r="M55" s="5">
+        <v>11086.040000000001</v>
+      </c>
+      <c r="N55" s="6">
+        <v>113</v>
+      </c>
+      <c r="O55" s="6">
+        <v>94</v>
+      </c>
+      <c r="P55" s="7">
+        <v>3.3146172131147544</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>27.214154794520546</v>
+      </c>
+      <c r="R55" s="8">
+        <v>17.228009722222222</v>
+      </c>
+      <c r="S55" s="8">
+        <v>7</v>
+      </c>
+      <c r="T55" s="9">
+        <v>0.12328767123287671</v>
+      </c>
+      <c r="U55" s="9">
+        <v>0.36170212765957449</v>
+      </c>
+      <c r="V55" s="9">
+        <v>0</v>
+      </c>
+      <c r="W55" s="9">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9">
+        <v>0.010638297872340425</v>
+      </c>
+      <c r="Y55" s="9">
+        <v>0.010638297872340425</v>
+      </c>
+      <c r="Z55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="9">
+        <v>0.010638297872340425</v>
+      </c>
+      <c r="AB55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="9">
+        <v>0.35106382978723405</v>
+      </c>
+      <c r="AD55" s="6">
+        <v>36</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>34</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="6">
+        <v>33</v>
+      </c>
+      <c r="AN55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP55" s="4">
         <v>58</v>
       </c>
@@ -10155,7 +10503,7 @@
         <v>19625</v>
       </c>
       <c r="B62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C62" s="4">
         <v>51</v>
@@ -10185,35 +10533,93 @@
         <v>58</v>
       </c>
       <c r="L62" s="4"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="6"/>
-      <c r="O62" s="6"/>
-      <c r="P62" s="7"/>
-      <c r="Q62" s="8"/>
-      <c r="R62" s="8"/>
-      <c r="S62" s="8"/>
-      <c r="T62" s="9"/>
-      <c r="U62" s="9"/>
-      <c r="V62" s="9"/>
-      <c r="W62" s="9"/>
-      <c r="X62" s="9"/>
-      <c r="Y62" s="9"/>
-      <c r="Z62" s="9"/>
-      <c r="AA62" s="9"/>
-      <c r="AB62" s="9"/>
-      <c r="AC62" s="9"/>
-      <c r="AD62" s="6"/>
-      <c r="AE62" s="6"/>
-      <c r="AF62" s="6"/>
-      <c r="AG62" s="6"/>
-      <c r="AH62" s="6"/>
-      <c r="AI62" s="6"/>
-      <c r="AJ62" s="6"/>
-      <c r="AK62" s="6"/>
-      <c r="AL62" s="6"/>
-      <c r="AM62" s="6"/>
-      <c r="AN62" s="9"/>
-      <c r="AO62" s="6"/>
+      <c r="M62" s="5">
+        <v>10674.99</v>
+      </c>
+      <c r="N62" s="6">
+        <v>102</v>
+      </c>
+      <c r="O62" s="6">
+        <v>63</v>
+      </c>
+      <c r="P62" s="7">
+        <v>3.3711970873786408</v>
+      </c>
+      <c r="Q62" s="8">
+        <v>14.002115873015873</v>
+      </c>
+      <c r="R62" s="8">
+        <v>3.9558333333333331</v>
+      </c>
+      <c r="S62" s="8">
+        <v>7</v>
+      </c>
+      <c r="T62" s="9">
+        <v>0.68253968253968256</v>
+      </c>
+      <c r="U62" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="V62" s="9">
+        <v>0</v>
+      </c>
+      <c r="W62" s="9">
+        <v>0.031746031745999999</v>
+      </c>
+      <c r="X62" s="9">
+        <v>0.031746031746031744</v>
+      </c>
+      <c r="Y62" s="9">
+        <v>0.031746031746031744</v>
+      </c>
+      <c r="Z62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="AB62" s="9">
+        <v>0.031746031746031744</v>
+      </c>
+      <c r="AC62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AH62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP62" s="4">
         <v>58</v>
       </c>
@@ -11231,7 +11637,7 @@
         <v>19648</v>
       </c>
       <c r="B70" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C70" s="4">
         <v>51</v>
@@ -11261,35 +11667,93 @@
         <v>58</v>
       </c>
       <c r="L70" s="4"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="6"/>
-      <c r="O70" s="6"/>
-      <c r="P70" s="7"/>
-      <c r="Q70" s="8"/>
-      <c r="R70" s="8"/>
-      <c r="S70" s="8"/>
-      <c r="T70" s="9"/>
-      <c r="U70" s="9"/>
-      <c r="V70" s="9"/>
-      <c r="W70" s="9"/>
-      <c r="X70" s="9"/>
-      <c r="Y70" s="9"/>
-      <c r="Z70" s="9"/>
-      <c r="AA70" s="9"/>
-      <c r="AB70" s="9"/>
-      <c r="AC70" s="9"/>
-      <c r="AD70" s="6"/>
-      <c r="AE70" s="6"/>
-      <c r="AF70" s="6"/>
-      <c r="AG70" s="6"/>
-      <c r="AH70" s="6"/>
-      <c r="AI70" s="6"/>
-      <c r="AJ70" s="6"/>
-      <c r="AK70" s="6"/>
-      <c r="AL70" s="6"/>
-      <c r="AM70" s="6"/>
-      <c r="AN70" s="9"/>
-      <c r="AO70" s="6"/>
+      <c r="M70" s="5">
+        <v>10715.74</v>
+      </c>
+      <c r="N70" s="6">
+        <v>118</v>
+      </c>
+      <c r="O70" s="6">
+        <v>77</v>
+      </c>
+      <c r="P70" s="7">
+        <v>5.0979887931034487</v>
+      </c>
+      <c r="Q70" s="8">
+        <v>20.541558441558443</v>
+      </c>
+      <c r="R70" s="8">
+        <v>8.1266233766233764</v>
+      </c>
+      <c r="S70" s="8">
+        <v>7</v>
+      </c>
+      <c r="T70" s="9">
+        <v>0.16883116883116883</v>
+      </c>
+      <c r="U70" s="9">
+        <v>0.025974025974025976</v>
+      </c>
+      <c r="V70" s="9">
+        <v>0</v>
+      </c>
+      <c r="W70" s="9">
+        <v>0</v>
+      </c>
+      <c r="X70" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="9">
+        <v>0.025974025974025976</v>
+      </c>
+      <c r="AC70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE70" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP70" s="4">
         <v>58</v>
       </c>
@@ -11330,7 +11794,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>51</v>
@@ -11358,35 +11822,93 @@
         <v>58</v>
       </c>
       <c r="L71" s="4"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="6"/>
-      <c r="O71" s="6"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="8"/>
-      <c r="S71" s="8"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
-      <c r="V71" s="9"/>
-      <c r="W71" s="9"/>
-      <c r="X71" s="9"/>
-      <c r="Y71" s="9"/>
-      <c r="Z71" s="9"/>
-      <c r="AA71" s="9"/>
-      <c r="AB71" s="9"/>
-      <c r="AC71" s="9"/>
-      <c r="AD71" s="6"/>
-      <c r="AE71" s="6"/>
-      <c r="AF71" s="6"/>
-      <c r="AG71" s="6"/>
-      <c r="AH71" s="6"/>
-      <c r="AI71" s="6"/>
-      <c r="AJ71" s="6"/>
-      <c r="AK71" s="6"/>
-      <c r="AL71" s="6"/>
-      <c r="AM71" s="6"/>
-      <c r="AN71" s="9"/>
-      <c r="AO71" s="6"/>
+      <c r="M71" s="5">
+        <v>12083.43</v>
+      </c>
+      <c r="N71" s="6">
+        <v>132</v>
+      </c>
+      <c r="O71" s="6">
+        <v>70</v>
+      </c>
+      <c r="P71" s="7">
+        <v>3.6372700787401571</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>14.02</v>
+      </c>
+      <c r="R71" s="8">
+        <v>2.8817703125</v>
+      </c>
+      <c r="S71" s="8">
+        <v>8</v>
+      </c>
+      <c r="T71" s="9">
+        <v>0.62857142857142856</v>
+      </c>
+      <c r="U71" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="V71" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="W71" s="9">
+        <v>0</v>
+      </c>
+      <c r="X71" s="9">
+        <v>0.085714285714285715</v>
+      </c>
+      <c r="Y71" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="Z71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="9">
+        <v>0.17142857142857143</v>
+      </c>
+      <c r="AB71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="9">
+        <v>0.11428571428571428</v>
+      </c>
+      <c r="AD71" s="6">
+        <v>30</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF71" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI71" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="6">
+        <v>12</v>
+      </c>
+      <c r="AL71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP71" s="4">
         <v>58</v>
       </c>
@@ -11834,7 +12356,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>51</v>
@@ -11864,35 +12386,93 @@
         <v>58</v>
       </c>
       <c r="L75" s="4"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
-      <c r="S75" s="8"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
-      <c r="AA75" s="9"/>
-      <c r="AB75" s="9"/>
-      <c r="AC75" s="9"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="6"/>
-      <c r="AN75" s="9"/>
-      <c r="AO75" s="6"/>
+      <c r="M75" s="5">
+        <v>9492.0799999999999</v>
+      </c>
+      <c r="N75" s="6">
+        <v>104</v>
+      </c>
+      <c r="O75" s="6">
+        <v>57</v>
+      </c>
+      <c r="P75" s="7">
+        <v>5.3608417475728158</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>28.86578947368421</v>
+      </c>
+      <c r="R75" s="8">
+        <v>17.209696363636365</v>
+      </c>
+      <c r="S75" s="8">
+        <v>7</v>
+      </c>
+      <c r="T75" s="9">
+        <v>0.070175438596491224</v>
+      </c>
+      <c r="U75" s="9">
+        <v>0.31578947368421051</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0.017543859649000001</v>
+      </c>
+      <c r="X75" s="9">
+        <v>0.08771929824561403</v>
+      </c>
+      <c r="Y75" s="9">
+        <v>0.035087719298245612</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0.035087719298245612</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>0.12280701754385964</v>
+      </c>
+      <c r="AC75" s="9">
+        <v>0.14035087719298245</v>
+      </c>
+      <c r="AD75" s="6">
+        <v>24</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>18</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH75" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI75" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>7</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP75" s="4">
         <v>58</v>
       </c>
@@ -12497,7 +13077,7 @@
         <v>19674</v>
       </c>
       <c r="B80" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C80" s="4">
         <v>51</v>
@@ -12525,35 +13105,93 @@
         <v>58</v>
       </c>
       <c r="L80" s="4"/>
-      <c r="M80" s="5"/>
-      <c r="N80" s="6"/>
-      <c r="O80" s="6"/>
-      <c r="P80" s="7"/>
-      <c r="Q80" s="8"/>
-      <c r="R80" s="8"/>
-      <c r="S80" s="8"/>
-      <c r="T80" s="9"/>
-      <c r="U80" s="9"/>
-      <c r="V80" s="9"/>
-      <c r="W80" s="9"/>
-      <c r="X80" s="9"/>
-      <c r="Y80" s="9"/>
-      <c r="Z80" s="9"/>
-      <c r="AA80" s="9"/>
-      <c r="AB80" s="9"/>
-      <c r="AC80" s="9"/>
-      <c r="AD80" s="6"/>
-      <c r="AE80" s="6"/>
-      <c r="AF80" s="6"/>
-      <c r="AG80" s="6"/>
-      <c r="AH80" s="6"/>
-      <c r="AI80" s="6"/>
-      <c r="AJ80" s="6"/>
-      <c r="AK80" s="6"/>
-      <c r="AL80" s="6"/>
-      <c r="AM80" s="6"/>
-      <c r="AN80" s="9"/>
-      <c r="AO80" s="6"/>
+      <c r="M80" s="5">
+        <v>7836.7299999999996</v>
+      </c>
+      <c r="N80" s="6">
+        <v>87</v>
+      </c>
+      <c r="O80" s="6">
+        <v>66</v>
+      </c>
+      <c r="P80" s="7">
+        <v>4.5924238636363635</v>
+      </c>
+      <c r="Q80" s="8">
+        <v>18.536110606060607</v>
+      </c>
+      <c r="R80" s="8">
+        <v>4.4051080645161287</v>
+      </c>
+      <c r="S80" s="8">
+        <v>10</v>
+      </c>
+      <c r="T80" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U80" s="9">
+        <v>0.2878787878787879</v>
+      </c>
+      <c r="V80" s="9">
+        <v>0</v>
+      </c>
+      <c r="W80" s="9">
+        <v>0</v>
+      </c>
+      <c r="X80" s="9">
+        <v>0.015151515151515152</v>
+      </c>
+      <c r="Y80" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="9">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="AB80" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="AD80" s="6">
+        <v>19</v>
+      </c>
+      <c r="AE80" s="6">
+        <v>19</v>
+      </c>
+      <c r="AF80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK80" s="6">
+        <v>12</v>
+      </c>
+      <c r="AL80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM80" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN80" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO80" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP80" s="4">
         <v>58</v>
       </c>
@@ -13887,7 +14525,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>51</v>
@@ -13917,35 +14555,93 @@
         <v>58</v>
       </c>
       <c r="L90" s="4"/>
-      <c r="M90" s="5"/>
-      <c r="N90" s="6"/>
-      <c r="O90" s="6"/>
-      <c r="P90" s="7"/>
-      <c r="Q90" s="8"/>
-      <c r="R90" s="8"/>
-      <c r="S90" s="8"/>
-      <c r="T90" s="9"/>
-      <c r="U90" s="9"/>
-      <c r="V90" s="9"/>
-      <c r="W90" s="9"/>
-      <c r="X90" s="9"/>
-      <c r="Y90" s="9"/>
-      <c r="Z90" s="9"/>
-      <c r="AA90" s="9"/>
-      <c r="AB90" s="9"/>
-      <c r="AC90" s="9"/>
-      <c r="AD90" s="6"/>
-      <c r="AE90" s="6"/>
-      <c r="AF90" s="6"/>
-      <c r="AG90" s="6"/>
-      <c r="AH90" s="6"/>
-      <c r="AI90" s="6"/>
-      <c r="AJ90" s="6"/>
-      <c r="AK90" s="6"/>
-      <c r="AL90" s="6"/>
-      <c r="AM90" s="6"/>
-      <c r="AN90" s="9"/>
-      <c r="AO90" s="6"/>
+      <c r="M90" s="5">
+        <v>10156.68</v>
+      </c>
+      <c r="N90" s="6">
+        <v>106</v>
+      </c>
+      <c r="O90" s="6">
+        <v>80</v>
+      </c>
+      <c r="P90" s="7">
+        <v>28.146795192307692</v>
+      </c>
+      <c r="Q90" s="8">
+        <v>60.668750000000003</v>
+      </c>
+      <c r="R90" s="8">
+        <v>22.167088607594938</v>
+      </c>
+      <c r="S90" s="8">
+        <v>7</v>
+      </c>
+      <c r="T90" s="9">
+        <v>0.012500000000000001</v>
+      </c>
+      <c r="U90" s="9">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="V90" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="W90" s="9">
+        <v>0</v>
+      </c>
+      <c r="X90" s="9">
+        <v>0.012500000000000001</v>
+      </c>
+      <c r="Y90" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="9">
+        <v>0.012500000000000001</v>
+      </c>
+      <c r="AA90" s="9">
+        <v>0.012500000000000001</v>
+      </c>
+      <c r="AB90" s="9">
+        <v>0.012500000000000001</v>
+      </c>
+      <c r="AC90" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="AD90" s="6">
+        <v>36</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>34</v>
+      </c>
+      <c r="AF90" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ90" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK90" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL90" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM90" s="6">
+        <v>30</v>
+      </c>
+      <c r="AN90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO90" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP90" s="4">
         <v>58</v>
       </c>
@@ -14864,7 +15560,7 @@
         <v>19710</v>
       </c>
       <c r="B97" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C97" s="4">
         <v>51</v>
@@ -14894,35 +15590,93 @@
         <v>58</v>
       </c>
       <c r="L97" s="4"/>
-      <c r="M97" s="5"/>
-      <c r="N97" s="6"/>
-      <c r="O97" s="6"/>
-      <c r="P97" s="7"/>
-      <c r="Q97" s="8"/>
-      <c r="R97" s="8"/>
-      <c r="S97" s="8"/>
-      <c r="T97" s="9"/>
-      <c r="U97" s="9"/>
-      <c r="V97" s="9"/>
-      <c r="W97" s="9"/>
-      <c r="X97" s="9"/>
-      <c r="Y97" s="9"/>
-      <c r="Z97" s="9"/>
-      <c r="AA97" s="9"/>
-      <c r="AB97" s="9"/>
-      <c r="AC97" s="9"/>
-      <c r="AD97" s="6"/>
-      <c r="AE97" s="6"/>
-      <c r="AF97" s="6"/>
-      <c r="AG97" s="6"/>
-      <c r="AH97" s="6"/>
-      <c r="AI97" s="6"/>
-      <c r="AJ97" s="6"/>
-      <c r="AK97" s="6"/>
-      <c r="AL97" s="6"/>
-      <c r="AM97" s="6"/>
-      <c r="AN97" s="9"/>
-      <c r="AO97" s="6"/>
+      <c r="M97" s="5">
+        <v>8301.9400000000005</v>
+      </c>
+      <c r="N97" s="6">
+        <v>71</v>
+      </c>
+      <c r="O97" s="6">
+        <v>44</v>
+      </c>
+      <c r="P97" s="7">
+        <v>8.2044605633802821</v>
+      </c>
+      <c r="Q97" s="8">
+        <v>16.957954545454545</v>
+      </c>
+      <c r="R97" s="8">
+        <v>1.5420642857142857</v>
+      </c>
+      <c r="S97" s="8">
+        <v>6</v>
+      </c>
+      <c r="T97" s="9">
+        <v>0.43181818181818182</v>
+      </c>
+      <c r="U97" s="9">
+        <v>0.11363636363636363</v>
+      </c>
+      <c r="V97" s="9">
+        <v>0</v>
+      </c>
+      <c r="W97" s="9">
+        <v>0</v>
+      </c>
+      <c r="X97" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="9">
+        <v>0.11363636363636363</v>
+      </c>
+      <c r="AB97" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE97" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP97" s="4">
         <v>58</v>
       </c>
@@ -15275,7 +16029,7 @@
         <v>19715</v>
       </c>
       <c r="B100" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C100" s="4">
         <v>51</v>
@@ -15305,35 +16059,93 @@
         <v>58</v>
       </c>
       <c r="L100" s="4"/>
-      <c r="M100" s="5"/>
-      <c r="N100" s="6"/>
-      <c r="O100" s="6"/>
-      <c r="P100" s="7"/>
-      <c r="Q100" s="8"/>
-      <c r="R100" s="8"/>
-      <c r="S100" s="8"/>
-      <c r="T100" s="9"/>
-      <c r="U100" s="9"/>
-      <c r="V100" s="9"/>
-      <c r="W100" s="9"/>
-      <c r="X100" s="9"/>
-      <c r="Y100" s="9"/>
-      <c r="Z100" s="9"/>
-      <c r="AA100" s="9"/>
-      <c r="AB100" s="9"/>
-      <c r="AC100" s="9"/>
-      <c r="AD100" s="6"/>
-      <c r="AE100" s="6"/>
-      <c r="AF100" s="6"/>
-      <c r="AG100" s="6"/>
-      <c r="AH100" s="6"/>
-      <c r="AI100" s="6"/>
-      <c r="AJ100" s="6"/>
-      <c r="AK100" s="6"/>
-      <c r="AL100" s="6"/>
-      <c r="AM100" s="6"/>
-      <c r="AN100" s="9"/>
-      <c r="AO100" s="6"/>
+      <c r="M100" s="5">
+        <v>9569.0900000000001</v>
+      </c>
+      <c r="N100" s="6">
+        <v>88</v>
+      </c>
+      <c r="O100" s="6">
+        <v>55</v>
+      </c>
+      <c r="P100" s="7">
+        <v>11.2524625</v>
+      </c>
+      <c r="Q100" s="8">
+        <v>30.764849090909092</v>
+      </c>
+      <c r="R100" s="8">
+        <v>9.5348759259259257</v>
+      </c>
+      <c r="S100" s="8">
+        <v>9</v>
+      </c>
+      <c r="T100" s="9">
+        <v>0.12727272727272726</v>
+      </c>
+      <c r="U100" s="9">
+        <v>0.25454545454545452</v>
+      </c>
+      <c r="V100" s="9">
+        <v>0</v>
+      </c>
+      <c r="W100" s="9">
+        <v>0</v>
+      </c>
+      <c r="X100" s="9">
+        <v>0.10909090909090909</v>
+      </c>
+      <c r="Y100" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="9">
+        <v>0.018181818181818181</v>
+      </c>
+      <c r="AB100" s="9">
+        <v>0.10909090909090909</v>
+      </c>
+      <c r="AC100" s="9">
+        <v>0.036363636363636362</v>
+      </c>
+      <c r="AD100" s="6">
+        <v>15</v>
+      </c>
+      <c r="AE100" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF100" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI100" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL100" s="6">
+        <v>6</v>
+      </c>
+      <c r="AM100" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN100" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO100" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP100" s="4">
         <v>58</v>
       </c>
@@ -15529,7 +16341,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -15559,35 +16371,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>8581.4500000000007</v>
+      </c>
+      <c r="N102" s="6">
+        <v>89</v>
+      </c>
+      <c r="O102" s="6">
+        <v>67</v>
+      </c>
+      <c r="P102" s="7">
+        <v>12.447282608695653</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>74.256313636363629</v>
+      </c>
+      <c r="R102" s="8">
+        <v>59.513934426229504</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.060606060606060608</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.31343283582089554</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0.014925373134328358</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0.044776119401999999</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.014925373134328358</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.044776119402985072</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.074626865671641784</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0.014925373134328358</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.22388059701492538</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>26</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>21</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>15</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -15628,7 +16498,7 @@
         <v>19720</v>
       </c>
       <c r="B103" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C103" s="4">
         <v>51</v>
@@ -15658,35 +16528,93 @@
         <v>58</v>
       </c>
       <c r="L103" s="4"/>
-      <c r="M103" s="5"/>
-      <c r="N103" s="6"/>
-      <c r="O103" s="6"/>
-      <c r="P103" s="7"/>
-      <c r="Q103" s="8"/>
-      <c r="R103" s="8"/>
-      <c r="S103" s="8"/>
-      <c r="T103" s="9"/>
-      <c r="U103" s="9"/>
-      <c r="V103" s="9"/>
-      <c r="W103" s="9"/>
-      <c r="X103" s="9"/>
-      <c r="Y103" s="9"/>
-      <c r="Z103" s="9"/>
-      <c r="AA103" s="9"/>
-      <c r="AB103" s="9"/>
-      <c r="AC103" s="9"/>
-      <c r="AD103" s="6"/>
-      <c r="AE103" s="6"/>
-      <c r="AF103" s="6"/>
-      <c r="AG103" s="6"/>
-      <c r="AH103" s="6"/>
-      <c r="AI103" s="6"/>
-      <c r="AJ103" s="6"/>
-      <c r="AK103" s="6"/>
-      <c r="AL103" s="6"/>
-      <c r="AM103" s="6"/>
-      <c r="AN103" s="9"/>
-      <c r="AO103" s="6"/>
+      <c r="M103" s="5">
+        <v>8945.2600000000002</v>
+      </c>
+      <c r="N103" s="6">
+        <v>92</v>
+      </c>
+      <c r="O103" s="6">
+        <v>73</v>
+      </c>
+      <c r="P103" s="7">
+        <v>6.8994505494505498</v>
+      </c>
+      <c r="Q103" s="8">
+        <v>15.264839726027397</v>
+      </c>
+      <c r="R103" s="8">
+        <v>2.5736111111111111</v>
+      </c>
+      <c r="S103" s="8">
+        <v>6</v>
+      </c>
+      <c r="T103" s="9">
+        <v>0.50684931506849318</v>
+      </c>
+      <c r="U103" s="9">
+        <v>0.068493150684931503</v>
+      </c>
+      <c r="V103" s="9">
+        <v>0.013698630136986301</v>
+      </c>
+      <c r="W103" s="9">
+        <v>0</v>
+      </c>
+      <c r="X103" s="9">
+        <v>0.027397260273972601</v>
+      </c>
+      <c r="Y103" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="9">
+        <v>0.041095890410958902</v>
+      </c>
+      <c r="AB103" s="9">
+        <v>0.013698630136986301</v>
+      </c>
+      <c r="AC103" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE103" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF103" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG103" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH103" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI103" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ103" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK103" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL103" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM103" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN103" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO103" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP103" s="4">
         <v>58</v>
       </c>
@@ -15727,7 +16655,7 @@
         <v>19721</v>
       </c>
       <c r="B104" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C104" s="4">
         <v>51</v>
@@ -15757,35 +16685,93 @@
         <v>58</v>
       </c>
       <c r="L104" s="4"/>
-      <c r="M104" s="5"/>
-      <c r="N104" s="6"/>
-      <c r="O104" s="6"/>
-      <c r="P104" s="7"/>
-      <c r="Q104" s="8"/>
-      <c r="R104" s="8"/>
-      <c r="S104" s="8"/>
-      <c r="T104" s="9"/>
-      <c r="U104" s="9"/>
-      <c r="V104" s="9"/>
-      <c r="W104" s="9"/>
-      <c r="X104" s="9"/>
-      <c r="Y104" s="9"/>
-      <c r="Z104" s="9"/>
-      <c r="AA104" s="9"/>
-      <c r="AB104" s="9"/>
-      <c r="AC104" s="9"/>
-      <c r="AD104" s="6"/>
-      <c r="AE104" s="6"/>
-      <c r="AF104" s="6"/>
-      <c r="AG104" s="6"/>
-      <c r="AH104" s="6"/>
-      <c r="AI104" s="6"/>
-      <c r="AJ104" s="6"/>
-      <c r="AK104" s="6"/>
-      <c r="AL104" s="6"/>
-      <c r="AM104" s="6"/>
-      <c r="AN104" s="9"/>
-      <c r="AO104" s="6"/>
+      <c r="M104" s="5">
+        <v>9146.9400000000005</v>
+      </c>
+      <c r="N104" s="6">
+        <v>93</v>
+      </c>
+      <c r="O104" s="6">
+        <v>49</v>
+      </c>
+      <c r="P104" s="7">
+        <v>4.7216849462365591</v>
+      </c>
+      <c r="Q104" s="8">
+        <v>17.28265306122449</v>
+      </c>
+      <c r="R104" s="8">
+        <v>4.5429622222222221</v>
+      </c>
+      <c r="S104" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="T104" s="9">
+        <v>0.36734693877551022</v>
+      </c>
+      <c r="U104" s="9">
+        <v>0.24489795918367346</v>
+      </c>
+      <c r="V104" s="9">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="W104" s="9">
+        <v>0</v>
+      </c>
+      <c r="X104" s="9">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="Y104" s="9">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="Z104" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA104" s="9">
+        <v>0.10204081632653061</v>
+      </c>
+      <c r="AB104" s="9">
+        <v>0.020408163265306121</v>
+      </c>
+      <c r="AC104" s="9">
+        <v>0.081632653061224483</v>
+      </c>
+      <c r="AD104" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE104" s="6">
+        <v>12</v>
+      </c>
+      <c r="AF104" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG104" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH104" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI104" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ104" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK104" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL104" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM104" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN104" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO104" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP104" s="4">
         <v>58</v>
       </c>
@@ -17410,7 +18396,7 @@
         <v>19745</v>
       </c>
       <c r="B117" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C117" s="4">
         <v>51</v>
@@ -17440,35 +18426,93 @@
         <v>58</v>
       </c>
       <c r="L117" s="4"/>
-      <c r="M117" s="5"/>
-      <c r="N117" s="6"/>
-      <c r="O117" s="6"/>
-      <c r="P117" s="7"/>
-      <c r="Q117" s="8"/>
-      <c r="R117" s="8"/>
-      <c r="S117" s="8"/>
-      <c r="T117" s="9"/>
-      <c r="U117" s="9"/>
-      <c r="V117" s="9"/>
-      <c r="W117" s="9"/>
-      <c r="X117" s="9"/>
-      <c r="Y117" s="9"/>
-      <c r="Z117" s="9"/>
-      <c r="AA117" s="9"/>
-      <c r="AB117" s="9"/>
-      <c r="AC117" s="9"/>
-      <c r="AD117" s="6"/>
-      <c r="AE117" s="6"/>
-      <c r="AF117" s="6"/>
-      <c r="AG117" s="6"/>
-      <c r="AH117" s="6"/>
-      <c r="AI117" s="6"/>
-      <c r="AJ117" s="6"/>
-      <c r="AK117" s="6"/>
-      <c r="AL117" s="6"/>
-      <c r="AM117" s="6"/>
-      <c r="AN117" s="9"/>
-      <c r="AO117" s="6"/>
+      <c r="M117" s="5">
+        <v>10504.99</v>
+      </c>
+      <c r="N117" s="6">
+        <v>106</v>
+      </c>
+      <c r="O117" s="6">
+        <v>75</v>
+      </c>
+      <c r="P117" s="7">
+        <v>5.113592233009709</v>
+      </c>
+      <c r="Q117" s="8">
+        <v>14.341777333333333</v>
+      </c>
+      <c r="R117" s="8">
+        <v>8.3135135135135148</v>
+      </c>
+      <c r="S117" s="8">
+        <v>7</v>
+      </c>
+      <c r="T117" s="9">
+        <v>0.71999999999999997</v>
+      </c>
+      <c r="U117" s="9">
+        <v>0.71999999999999997</v>
+      </c>
+      <c r="V117" s="9">
+        <v>0</v>
+      </c>
+      <c r="W117" s="9">
+        <v>0</v>
+      </c>
+      <c r="X117" s="9">
+        <v>0.026666666666666668</v>
+      </c>
+      <c r="Y117" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="Z117" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA117" s="9">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AB117" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AC117" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="AD117" s="6">
+        <v>87</v>
+      </c>
+      <c r="AE117" s="6">
+        <v>54</v>
+      </c>
+      <c r="AF117" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG117" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH117" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI117" s="6">
+        <v>10</v>
+      </c>
+      <c r="AJ117" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK117" s="6">
+        <v>42</v>
+      </c>
+      <c r="AL117" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM117" s="6">
+        <v>30</v>
+      </c>
+      <c r="AN117" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO117" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP117" s="4">
         <v>58</v>
       </c>
@@ -18445,7 +19489,7 @@
         <v>19755</v>
       </c>
       <c r="B124" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C124" s="4">
         <v>51</v>
@@ -18475,35 +19519,93 @@
         <v>58</v>
       </c>
       <c r="L124" s="4"/>
-      <c r="M124" s="5"/>
-      <c r="N124" s="6"/>
-      <c r="O124" s="6"/>
-      <c r="P124" s="7"/>
-      <c r="Q124" s="8"/>
-      <c r="R124" s="8"/>
-      <c r="S124" s="8"/>
-      <c r="T124" s="9"/>
-      <c r="U124" s="9"/>
-      <c r="V124" s="9"/>
-      <c r="W124" s="9"/>
-      <c r="X124" s="9"/>
-      <c r="Y124" s="9"/>
-      <c r="Z124" s="9"/>
-      <c r="AA124" s="9"/>
-      <c r="AB124" s="9"/>
-      <c r="AC124" s="9"/>
-      <c r="AD124" s="6"/>
-      <c r="AE124" s="6"/>
-      <c r="AF124" s="6"/>
-      <c r="AG124" s="6"/>
-      <c r="AH124" s="6"/>
-      <c r="AI124" s="6"/>
-      <c r="AJ124" s="6"/>
-      <c r="AK124" s="6"/>
-      <c r="AL124" s="6"/>
-      <c r="AM124" s="6"/>
-      <c r="AN124" s="9"/>
-      <c r="AO124" s="6"/>
+      <c r="M124" s="5">
+        <v>5044.1800000000003</v>
+      </c>
+      <c r="N124" s="6">
+        <v>36</v>
+      </c>
+      <c r="O124" s="6">
+        <v>24</v>
+      </c>
+      <c r="P124" s="7">
+        <v>10.852439024390243</v>
+      </c>
+      <c r="Q124" s="8">
+        <v>46.902899999999995</v>
+      </c>
+      <c r="R124" s="8">
+        <v>27.824639130434779</v>
+      </c>
+      <c r="S124" s="8">
+        <v>8</v>
+      </c>
+      <c r="T124" s="9">
+        <v>0</v>
+      </c>
+      <c r="U124" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="V124" s="9">
+        <v>0</v>
+      </c>
+      <c r="W124" s="9">
+        <v>0</v>
+      </c>
+      <c r="X124" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y124" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z124" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AA124" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB124" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC124" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD124" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE124" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF124" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG124" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH124" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI124" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ124" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK124" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL124" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM124" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN124" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO124" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP124" s="4">
         <v>58</v>
       </c>
@@ -18701,7 +19803,7 @@
         <v>19759</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C126" s="4">
         <v>51</v>
@@ -18731,35 +19833,93 @@
         <v>58</v>
       </c>
       <c r="L126" s="4"/>
-      <c r="M126" s="5"/>
-      <c r="N126" s="6"/>
-      <c r="O126" s="6"/>
-      <c r="P126" s="7"/>
-      <c r="Q126" s="8"/>
-      <c r="R126" s="8"/>
-      <c r="S126" s="8"/>
-      <c r="T126" s="9"/>
-      <c r="U126" s="9"/>
-      <c r="V126" s="9"/>
-      <c r="W126" s="9"/>
-      <c r="X126" s="9"/>
-      <c r="Y126" s="9"/>
-      <c r="Z126" s="9"/>
-      <c r="AA126" s="9"/>
-      <c r="AB126" s="9"/>
-      <c r="AC126" s="9"/>
-      <c r="AD126" s="6"/>
-      <c r="AE126" s="6"/>
-      <c r="AF126" s="6"/>
-      <c r="AG126" s="6"/>
-      <c r="AH126" s="6"/>
-      <c r="AI126" s="6"/>
-      <c r="AJ126" s="6"/>
-      <c r="AK126" s="6"/>
-      <c r="AL126" s="6"/>
-      <c r="AM126" s="6"/>
-      <c r="AN126" s="9"/>
-      <c r="AO126" s="6"/>
+      <c r="M126" s="5">
+        <v>5376.1400000000003</v>
+      </c>
+      <c r="N126" s="6">
+        <v>64</v>
+      </c>
+      <c r="O126" s="6">
+        <v>38</v>
+      </c>
+      <c r="P126" s="7">
+        <v>6.5187184615384615</v>
+      </c>
+      <c r="Q126" s="8">
+        <v>30.306139473684208</v>
+      </c>
+      <c r="R126" s="8">
+        <v>17.347297297297299</v>
+      </c>
+      <c r="S126" s="8">
+        <v>7</v>
+      </c>
+      <c r="T126" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="U126" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="V126" s="9">
+        <v>0</v>
+      </c>
+      <c r="W126" s="9">
+        <v>0</v>
+      </c>
+      <c r="X126" s="9">
+        <v>0.026315789473684209</v>
+      </c>
+      <c r="Y126" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA126" s="9">
+        <v>0.026315789473684209</v>
+      </c>
+      <c r="AB126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD126" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH126" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK126" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO126" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP126" s="4">
         <v>58</v>
       </c>
@@ -22698,7 +23858,7 @@
         <v>19842</v>
       </c>
       <c r="B153" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C153" s="4">
         <v>51</v>
@@ -22728,35 +23888,93 @@
         <v>58</v>
       </c>
       <c r="L153" s="4"/>
-      <c r="M153" s="5"/>
-      <c r="N153" s="6"/>
-      <c r="O153" s="6"/>
-      <c r="P153" s="7"/>
-      <c r="Q153" s="8"/>
-      <c r="R153" s="8"/>
-      <c r="S153" s="8"/>
-      <c r="T153" s="9"/>
-      <c r="U153" s="9"/>
-      <c r="V153" s="9"/>
-      <c r="W153" s="9"/>
-      <c r="X153" s="9"/>
-      <c r="Y153" s="9"/>
-      <c r="Z153" s="9"/>
-      <c r="AA153" s="9"/>
-      <c r="AB153" s="9"/>
-      <c r="AC153" s="9"/>
-      <c r="AD153" s="6"/>
-      <c r="AE153" s="6"/>
-      <c r="AF153" s="6"/>
-      <c r="AG153" s="6"/>
-      <c r="AH153" s="6"/>
-      <c r="AI153" s="6"/>
-      <c r="AJ153" s="6"/>
-      <c r="AK153" s="6"/>
-      <c r="AL153" s="6"/>
-      <c r="AM153" s="6"/>
-      <c r="AN153" s="9"/>
-      <c r="AO153" s="6"/>
+      <c r="M153" s="5">
+        <v>16813.790000000001</v>
+      </c>
+      <c r="N153" s="6">
+        <v>159</v>
+      </c>
+      <c r="O153" s="6">
+        <v>108</v>
+      </c>
+      <c r="P153" s="7">
+        <v>5.508064516129032</v>
+      </c>
+      <c r="Q153" s="8">
+        <v>22.291049074074074</v>
+      </c>
+      <c r="R153" s="8">
+        <v>9.1209122641509435</v>
+      </c>
+      <c r="S153" s="8">
+        <v>8</v>
+      </c>
+      <c r="T153" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U153" s="9">
+        <v>0.046296296296296294</v>
+      </c>
+      <c r="V153" s="9">
+        <v>0</v>
+      </c>
+      <c r="W153" s="9">
+        <v>0</v>
+      </c>
+      <c r="X153" s="9">
+        <v>0.0092592592592592587</v>
+      </c>
+      <c r="Y153" s="9">
+        <v>0.0092592592592592587</v>
+      </c>
+      <c r="Z153" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA153" s="9">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="AB153" s="9">
+        <v>0.018518518518518517</v>
+      </c>
+      <c r="AC153" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD153" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE153" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF153" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG153" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH153" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI153" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ153" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK153" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL153" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM153" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN153" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO153" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP153" s="4">
         <v>58</v>
       </c>
@@ -23877,7 +25095,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>51</v>
@@ -23907,35 +25125,93 @@
         <v>58</v>
       </c>
       <c r="L162" s="4"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="6"/>
-      <c r="O162" s="6"/>
-      <c r="P162" s="7"/>
-      <c r="Q162" s="8"/>
-      <c r="R162" s="8"/>
-      <c r="S162" s="8"/>
-      <c r="T162" s="9"/>
-      <c r="U162" s="9"/>
-      <c r="V162" s="9"/>
-      <c r="W162" s="9"/>
-      <c r="X162" s="9"/>
-      <c r="Y162" s="9"/>
-      <c r="Z162" s="9"/>
-      <c r="AA162" s="9"/>
-      <c r="AB162" s="9"/>
-      <c r="AC162" s="9"/>
-      <c r="AD162" s="6"/>
-      <c r="AE162" s="6"/>
-      <c r="AF162" s="6"/>
-      <c r="AG162" s="6"/>
-      <c r="AH162" s="6"/>
-      <c r="AI162" s="6"/>
-      <c r="AJ162" s="6"/>
-      <c r="AK162" s="6"/>
-      <c r="AL162" s="6"/>
-      <c r="AM162" s="6"/>
-      <c r="AN162" s="9"/>
-      <c r="AO162" s="6"/>
+      <c r="M162" s="5">
+        <v>8704.9099999999999</v>
+      </c>
+      <c r="N162" s="6">
+        <v>88</v>
+      </c>
+      <c r="O162" s="6">
+        <v>57</v>
+      </c>
+      <c r="P162" s="7">
+        <v>5.5606421686746987</v>
+      </c>
+      <c r="Q162" s="8">
+        <v>23.502338596491228</v>
+      </c>
+      <c r="R162" s="8">
+        <v>10.281871929824561</v>
+      </c>
+      <c r="S162" s="8">
+        <v>8</v>
+      </c>
+      <c r="T162" s="9">
+        <v>0.12280701754385964</v>
+      </c>
+      <c r="U162" s="9">
+        <v>0.47368421052631576</v>
+      </c>
+      <c r="V162" s="9">
+        <v>0</v>
+      </c>
+      <c r="W162" s="9">
+        <v>0.017543859649000001</v>
+      </c>
+      <c r="X162" s="9">
+        <v>0.070175438596491224</v>
+      </c>
+      <c r="Y162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC162" s="9">
+        <v>0.42105263157894735</v>
+      </c>
+      <c r="AD162" s="6">
+        <v>28</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>27</v>
+      </c>
+      <c r="AF162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH162" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM162" s="6">
+        <v>24</v>
+      </c>
+      <c r="AN162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO162" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP162" s="4">
         <v>58</v>
       </c>
@@ -25488,7 +26764,7 @@
         <v>19891</v>
       </c>
       <c r="B173" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C173" s="4">
         <v>51</v>
@@ -25518,35 +26794,93 @@
         <v>58</v>
       </c>
       <c r="L173" s="4"/>
-      <c r="M173" s="5"/>
-      <c r="N173" s="6"/>
-      <c r="O173" s="6"/>
-      <c r="P173" s="7"/>
-      <c r="Q173" s="8"/>
-      <c r="R173" s="8"/>
-      <c r="S173" s="8"/>
-      <c r="T173" s="9"/>
-      <c r="U173" s="9"/>
-      <c r="V173" s="9"/>
-      <c r="W173" s="9"/>
-      <c r="X173" s="9"/>
-      <c r="Y173" s="9"/>
-      <c r="Z173" s="9"/>
-      <c r="AA173" s="9"/>
-      <c r="AB173" s="9"/>
-      <c r="AC173" s="9"/>
-      <c r="AD173" s="6"/>
-      <c r="AE173" s="6"/>
-      <c r="AF173" s="6"/>
-      <c r="AG173" s="6"/>
-      <c r="AH173" s="6"/>
-      <c r="AI173" s="6"/>
-      <c r="AJ173" s="6"/>
-      <c r="AK173" s="6"/>
-      <c r="AL173" s="6"/>
-      <c r="AM173" s="6"/>
-      <c r="AN173" s="9"/>
-      <c r="AO173" s="6"/>
+      <c r="M173" s="5">
+        <v>4665.5</v>
+      </c>
+      <c r="N173" s="6">
+        <v>50</v>
+      </c>
+      <c r="O173" s="6">
+        <v>31</v>
+      </c>
+      <c r="P173" s="7">
+        <v>7.7221153846153845</v>
+      </c>
+      <c r="Q173" s="8">
+        <v>17.438170967741936</v>
+      </c>
+      <c r="R173" s="8">
+        <v>11.12262142857143</v>
+      </c>
+      <c r="S173" s="8">
+        <v>7</v>
+      </c>
+      <c r="T173" s="9">
+        <v>0.58064516129032262</v>
+      </c>
+      <c r="U173" s="9">
+        <v>0.70967741935483875</v>
+      </c>
+      <c r="V173" s="9">
+        <v>0</v>
+      </c>
+      <c r="W173" s="9">
+        <v>0</v>
+      </c>
+      <c r="X173" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y173" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="Z173" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA173" s="9">
+        <v>0.58064516129032262</v>
+      </c>
+      <c r="AB173" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC173" s="9">
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="AD173" s="6">
+        <v>25</v>
+      </c>
+      <c r="AE173" s="6">
+        <v>22</v>
+      </c>
+      <c r="AF173" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG173" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH173" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI173" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ173" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK173" s="6">
+        <v>18</v>
+      </c>
+      <c r="AL173" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM173" s="6">
+        <v>5</v>
+      </c>
+      <c r="AN173" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO173" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP173" s="4">
         <v>58</v>
       </c>
@@ -26632,7 +27966,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>51</v>
@@ -26662,35 +27996,93 @@
         <v>58</v>
       </c>
       <c r="L181" s="4"/>
-      <c r="M181" s="5"/>
-      <c r="N181" s="6"/>
-      <c r="O181" s="6"/>
-      <c r="P181" s="7"/>
-      <c r="Q181" s="8"/>
-      <c r="R181" s="8"/>
-      <c r="S181" s="8"/>
-      <c r="T181" s="9"/>
-      <c r="U181" s="9"/>
-      <c r="V181" s="9"/>
-      <c r="W181" s="9"/>
-      <c r="X181" s="9"/>
-      <c r="Y181" s="9"/>
-      <c r="Z181" s="9"/>
-      <c r="AA181" s="9"/>
-      <c r="AB181" s="9"/>
-      <c r="AC181" s="9"/>
-      <c r="AD181" s="6"/>
-      <c r="AE181" s="6"/>
-      <c r="AF181" s="6"/>
-      <c r="AG181" s="6"/>
-      <c r="AH181" s="6"/>
-      <c r="AI181" s="6"/>
-      <c r="AJ181" s="6"/>
-      <c r="AK181" s="6"/>
-      <c r="AL181" s="6"/>
-      <c r="AM181" s="6"/>
-      <c r="AN181" s="9"/>
-      <c r="AO181" s="6"/>
+      <c r="M181" s="5">
+        <v>5863.4200000000001</v>
+      </c>
+      <c r="N181" s="6">
+        <v>54</v>
+      </c>
+      <c r="O181" s="6">
+        <v>35</v>
+      </c>
+      <c r="P181" s="7">
+        <v>7.4714285714285706</v>
+      </c>
+      <c r="Q181" s="8">
+        <v>18.670951428571428</v>
+      </c>
+      <c r="R181" s="8">
+        <v>7.1826374999999993</v>
+      </c>
+      <c r="S181" s="8">
+        <v>8</v>
+      </c>
+      <c r="T181" s="9">
+        <v>0.37142857142857144</v>
+      </c>
+      <c r="U181" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="V181" s="9">
+        <v>0</v>
+      </c>
+      <c r="W181" s="9">
+        <v>0</v>
+      </c>
+      <c r="X181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="9">
+        <v>0.37142857142857144</v>
+      </c>
+      <c r="AB181" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="AC181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD181" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK181" s="6">
+        <v>13</v>
+      </c>
+      <c r="AL181" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP181" s="4">
         <v>58</v>
       </c>
@@ -26888,7 +28280,7 @@
         <v>19912</v>
       </c>
       <c r="B183" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C183" s="4">
         <v>51</v>
@@ -26918,35 +28310,93 @@
         <v>58</v>
       </c>
       <c r="L183" s="4"/>
-      <c r="M183" s="5"/>
-      <c r="N183" s="6"/>
-      <c r="O183" s="6"/>
-      <c r="P183" s="7"/>
-      <c r="Q183" s="8"/>
-      <c r="R183" s="8"/>
-      <c r="S183" s="8"/>
-      <c r="T183" s="9"/>
-      <c r="U183" s="9"/>
-      <c r="V183" s="9"/>
-      <c r="W183" s="9"/>
-      <c r="X183" s="9"/>
-      <c r="Y183" s="9"/>
-      <c r="Z183" s="9"/>
-      <c r="AA183" s="9"/>
-      <c r="AB183" s="9"/>
-      <c r="AC183" s="9"/>
-      <c r="AD183" s="6"/>
-      <c r="AE183" s="6"/>
-      <c r="AF183" s="6"/>
-      <c r="AG183" s="6"/>
-      <c r="AH183" s="6"/>
-      <c r="AI183" s="6"/>
-      <c r="AJ183" s="6"/>
-      <c r="AK183" s="6"/>
-      <c r="AL183" s="6"/>
-      <c r="AM183" s="6"/>
-      <c r="AN183" s="9"/>
-      <c r="AO183" s="6"/>
+      <c r="M183" s="5">
+        <v>5950.4300000000003</v>
+      </c>
+      <c r="N183" s="6">
+        <v>69</v>
+      </c>
+      <c r="O183" s="6">
+        <v>44</v>
+      </c>
+      <c r="P183" s="7">
+        <v>4.3182296874999997</v>
+      </c>
+      <c r="Q183" s="8">
+        <v>14.858334090909091</v>
+      </c>
+      <c r="R183" s="8">
+        <v>3.0890243902439027</v>
+      </c>
+      <c r="S183" s="8">
+        <v>8</v>
+      </c>
+      <c r="T183" s="9">
+        <v>0.61363636363636365</v>
+      </c>
+      <c r="U183" s="9">
+        <v>0.31818181818181818</v>
+      </c>
+      <c r="V183" s="9">
+        <v>0.068181818181818177</v>
+      </c>
+      <c r="W183" s="9">
+        <v>0</v>
+      </c>
+      <c r="X183" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="Y183" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA183" s="9">
+        <v>0.15909090909090909</v>
+      </c>
+      <c r="AB183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC183" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="AD183" s="6">
+        <v>18</v>
+      </c>
+      <c r="AE183" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF183" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH183" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK183" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM183" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO183" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP183" s="4">
         <v>58</v>
       </c>
@@ -27243,7 +28693,7 @@
         <v>19926</v>
       </c>
       <c r="B186" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C186" s="4">
         <v>51</v>
@@ -27273,35 +28723,93 @@
         <v>58</v>
       </c>
       <c r="L186" s="4"/>
-      <c r="M186" s="5"/>
-      <c r="N186" s="6"/>
-      <c r="O186" s="6"/>
-      <c r="P186" s="7"/>
-      <c r="Q186" s="8"/>
-      <c r="R186" s="8"/>
-      <c r="S186" s="8"/>
-      <c r="T186" s="9"/>
-      <c r="U186" s="9"/>
-      <c r="V186" s="9"/>
-      <c r="W186" s="9"/>
-      <c r="X186" s="9"/>
-      <c r="Y186" s="9"/>
-      <c r="Z186" s="9"/>
-      <c r="AA186" s="9"/>
-      <c r="AB186" s="9"/>
-      <c r="AC186" s="9"/>
-      <c r="AD186" s="6"/>
-      <c r="AE186" s="6"/>
-      <c r="AF186" s="6"/>
-      <c r="AG186" s="6"/>
-      <c r="AH186" s="6"/>
-      <c r="AI186" s="6"/>
-      <c r="AJ186" s="6"/>
-      <c r="AK186" s="6"/>
-      <c r="AL186" s="6"/>
-      <c r="AM186" s="6"/>
-      <c r="AN186" s="9"/>
-      <c r="AO186" s="6"/>
+      <c r="M186" s="5">
+        <v>3678.1900000000001</v>
+      </c>
+      <c r="N186" s="6">
+        <v>43</v>
+      </c>
+      <c r="O186" s="6">
+        <v>24</v>
+      </c>
+      <c r="P186" s="7">
+        <v>16.433334146341465</v>
+      </c>
+      <c r="Q186" s="8">
+        <v>48.136804166666671</v>
+      </c>
+      <c r="R186" s="8">
+        <v>22.663887500000001</v>
+      </c>
+      <c r="S186" s="8">
+        <v>7</v>
+      </c>
+      <c r="T186" s="9">
+        <v>0</v>
+      </c>
+      <c r="U186" s="9">
+        <v>0.625</v>
+      </c>
+      <c r="V186" s="9">
+        <v>0</v>
+      </c>
+      <c r="W186" s="9">
+        <v>0</v>
+      </c>
+      <c r="X186" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y186" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC186" s="9">
+        <v>0.625</v>
+      </c>
+      <c r="AD186" s="6">
+        <v>15</v>
+      </c>
+      <c r="AE186" s="6">
+        <v>15</v>
+      </c>
+      <c r="AF186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM186" s="6">
+        <v>15</v>
+      </c>
+      <c r="AN186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO186" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP186" s="4">
         <v>58</v>
       </c>
@@ -27342,7 +28850,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>51</v>
@@ -27372,35 +28880,93 @@
         <v>58</v>
       </c>
       <c r="L187" s="4"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="7"/>
-      <c r="Q187" s="8"/>
-      <c r="R187" s="8"/>
-      <c r="S187" s="8"/>
-      <c r="T187" s="9"/>
-      <c r="U187" s="9"/>
-      <c r="V187" s="9"/>
-      <c r="W187" s="9"/>
-      <c r="X187" s="9"/>
-      <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-      <c r="AA187" s="9"/>
-      <c r="AB187" s="9"/>
-      <c r="AC187" s="9"/>
-      <c r="AD187" s="6"/>
-      <c r="AE187" s="6"/>
-      <c r="AF187" s="6"/>
-      <c r="AG187" s="6"/>
-      <c r="AH187" s="6"/>
-      <c r="AI187" s="6"/>
-      <c r="AJ187" s="6"/>
-      <c r="AK187" s="6"/>
-      <c r="AL187" s="6"/>
-      <c r="AM187" s="6"/>
-      <c r="AN187" s="9"/>
-      <c r="AO187" s="6"/>
+      <c r="M187" s="5">
+        <v>1807.5999999999999</v>
+      </c>
+      <c r="N187" s="6">
+        <v>23</v>
+      </c>
+      <c r="O187" s="6">
+        <v>16</v>
+      </c>
+      <c r="P187" s="7">
+        <v>5.4463782608695652</v>
+      </c>
+      <c r="Q187" s="8">
+        <v>20.337499999999999</v>
+      </c>
+      <c r="R187" s="8">
+        <v>8.7277799999999992</v>
+      </c>
+      <c r="S187" s="8">
+        <v>7</v>
+      </c>
+      <c r="T187" s="9">
+        <v>0.3125</v>
+      </c>
+      <c r="U187" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="V187" s="9">
+        <v>0</v>
+      </c>
+      <c r="W187" s="9">
+        <v>0</v>
+      </c>
+      <c r="X187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP187" s="4">
         <v>58</v>
       </c>
@@ -27598,7 +29164,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>51</v>
@@ -27628,35 +29194,93 @@
         <v>58</v>
       </c>
       <c r="L189" s="4"/>
-      <c r="M189" s="5"/>
-      <c r="N189" s="6"/>
-      <c r="O189" s="6"/>
-      <c r="P189" s="7"/>
-      <c r="Q189" s="8"/>
-      <c r="R189" s="8"/>
-      <c r="S189" s="8"/>
-      <c r="T189" s="9"/>
-      <c r="U189" s="9"/>
-      <c r="V189" s="9"/>
-      <c r="W189" s="9"/>
-      <c r="X189" s="9"/>
-      <c r="Y189" s="9"/>
-      <c r="Z189" s="9"/>
-      <c r="AA189" s="9"/>
-      <c r="AB189" s="9"/>
-      <c r="AC189" s="9"/>
-      <c r="AD189" s="6"/>
-      <c r="AE189" s="6"/>
-      <c r="AF189" s="6"/>
-      <c r="AG189" s="6"/>
-      <c r="AH189" s="6"/>
-      <c r="AI189" s="6"/>
-      <c r="AJ189" s="6"/>
-      <c r="AK189" s="6"/>
-      <c r="AL189" s="6"/>
-      <c r="AM189" s="6"/>
-      <c r="AN189" s="9"/>
-      <c r="AO189" s="6"/>
+      <c r="M189" s="5">
+        <v>6288.96</v>
+      </c>
+      <c r="N189" s="6">
+        <v>73</v>
+      </c>
+      <c r="O189" s="6">
+        <v>65</v>
+      </c>
+      <c r="P189" s="7">
+        <v>5.1964439999999996</v>
+      </c>
+      <c r="Q189" s="8">
+        <v>29.141538461538463</v>
+      </c>
+      <c r="R189" s="8">
+        <v>21.039999999999999</v>
+      </c>
+      <c r="S189" s="8">
+        <v>7</v>
+      </c>
+      <c r="T189" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="U189" s="9">
+        <v>0.63076923076923075</v>
+      </c>
+      <c r="V189" s="9">
+        <v>0</v>
+      </c>
+      <c r="W189" s="9">
+        <v>0</v>
+      </c>
+      <c r="X189" s="9">
+        <v>0.030769230769230771</v>
+      </c>
+      <c r="Y189" s="9">
+        <v>0.061538461538461542</v>
+      </c>
+      <c r="Z189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9">
+        <v>0.16923076923076924</v>
+      </c>
+      <c r="AB189" s="9">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="AC189" s="9">
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="AD189" s="6">
+        <v>53</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>41</v>
+      </c>
+      <c r="AF189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH189" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI189" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK189" s="6">
+        <v>11</v>
+      </c>
+      <c r="AL189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM189" s="6">
+        <v>35</v>
+      </c>
+      <c r="AN189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO189" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP189" s="4">
         <v>58</v>
       </c>
@@ -27697,7 +29321,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>51</v>
@@ -27727,35 +29351,93 @@
         <v>58</v>
       </c>
       <c r="L190" s="4"/>
-      <c r="M190" s="5"/>
-      <c r="N190" s="6"/>
-      <c r="O190" s="6"/>
-      <c r="P190" s="7"/>
-      <c r="Q190" s="8"/>
-      <c r="R190" s="8"/>
-      <c r="S190" s="8"/>
-      <c r="T190" s="9"/>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
-      <c r="W190" s="9"/>
-      <c r="X190" s="9"/>
-      <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-      <c r="AA190" s="9"/>
-      <c r="AB190" s="9"/>
-      <c r="AC190" s="9"/>
-      <c r="AD190" s="6"/>
-      <c r="AE190" s="6"/>
-      <c r="AF190" s="6"/>
-      <c r="AG190" s="6"/>
-      <c r="AH190" s="6"/>
-      <c r="AI190" s="6"/>
-      <c r="AJ190" s="6"/>
-      <c r="AK190" s="6"/>
-      <c r="AL190" s="6"/>
-      <c r="AM190" s="6"/>
-      <c r="AN190" s="9"/>
-      <c r="AO190" s="6"/>
+      <c r="M190" s="5">
+        <v>5663.2200000000003</v>
+      </c>
+      <c r="N190" s="6">
+        <v>67</v>
+      </c>
+      <c r="O190" s="6">
+        <v>27</v>
+      </c>
+      <c r="P190" s="7">
+        <v>3.2702015151515154</v>
+      </c>
+      <c r="Q190" s="8">
+        <v>12.820988888888889</v>
+      </c>
+      <c r="R190" s="8">
+        <v>2.570988888888889</v>
+      </c>
+      <c r="S190" s="8">
+        <v>7</v>
+      </c>
+      <c r="T190" s="9">
+        <v>0.81481481481481477</v>
+      </c>
+      <c r="U190" s="9">
+        <v>0.18518518518518517</v>
+      </c>
+      <c r="V190" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="W190" s="9">
+        <v>0</v>
+      </c>
+      <c r="X190" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="AD190" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK190" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM190" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO190" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP190" s="4">
         <v>58</v>
       </c>
@@ -28110,7 +29792,7 @@
         <v>19940</v>
       </c>
       <c r="B193" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C193" s="4">
         <v>51</v>
@@ -28138,35 +29820,93 @@
         <v>58</v>
       </c>
       <c r="L193" s="4"/>
-      <c r="M193" s="5"/>
-      <c r="N193" s="6"/>
-      <c r="O193" s="6"/>
-      <c r="P193" s="7"/>
-      <c r="Q193" s="8"/>
-      <c r="R193" s="8"/>
-      <c r="S193" s="8"/>
-      <c r="T193" s="9"/>
-      <c r="U193" s="9"/>
-      <c r="V193" s="9"/>
-      <c r="W193" s="9"/>
-      <c r="X193" s="9"/>
-      <c r="Y193" s="9"/>
-      <c r="Z193" s="9"/>
-      <c r="AA193" s="9"/>
-      <c r="AB193" s="9"/>
-      <c r="AC193" s="9"/>
-      <c r="AD193" s="6"/>
-      <c r="AE193" s="6"/>
-      <c r="AF193" s="6"/>
-      <c r="AG193" s="6"/>
-      <c r="AH193" s="6"/>
-      <c r="AI193" s="6"/>
-      <c r="AJ193" s="6"/>
-      <c r="AK193" s="6"/>
-      <c r="AL193" s="6"/>
-      <c r="AM193" s="6"/>
-      <c r="AN193" s="9"/>
-      <c r="AO193" s="6"/>
+      <c r="M193" s="5">
+        <v>7956.4399999999996</v>
+      </c>
+      <c r="N193" s="6">
+        <v>93</v>
+      </c>
+      <c r="O193" s="6">
+        <v>52</v>
+      </c>
+      <c r="P193" s="7">
+        <v>7.5240243243243246</v>
+      </c>
+      <c r="Q193" s="8">
+        <v>20.031409615384614</v>
+      </c>
+      <c r="R193" s="8">
+        <v>7.8348477272727273</v>
+      </c>
+      <c r="S193" s="8">
+        <v>7</v>
+      </c>
+      <c r="T193" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="U193" s="9">
+        <v>0.42307692307692307</v>
+      </c>
+      <c r="V193" s="9">
+        <v>0</v>
+      </c>
+      <c r="W193" s="9">
+        <v>0</v>
+      </c>
+      <c r="X193" s="9">
+        <v>0.17307692307692307</v>
+      </c>
+      <c r="Y193" s="9">
+        <v>0.096153846153846159</v>
+      </c>
+      <c r="Z193" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="AA193" s="9">
+        <v>0.17307692307692307</v>
+      </c>
+      <c r="AB193" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AC193" s="9">
+        <v>0.28846153846153844</v>
+      </c>
+      <c r="AD193" s="6">
+        <v>41</v>
+      </c>
+      <c r="AE193" s="6">
+        <v>22</v>
+      </c>
+      <c r="AF193" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG193" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH193" s="6">
+        <v>9</v>
+      </c>
+      <c r="AI193" s="6">
+        <v>5</v>
+      </c>
+      <c r="AJ193" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK193" s="6">
+        <v>9</v>
+      </c>
+      <c r="AL193" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM193" s="6">
+        <v>15</v>
+      </c>
+      <c r="AN193" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO193" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP193" s="4">
         <v>58</v>
       </c>
@@ -28207,7 +29947,7 @@
         <v>19943</v>
       </c>
       <c r="B194" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C194" s="4">
         <v>51</v>
@@ -28237,35 +29977,93 @@
         <v>58</v>
       </c>
       <c r="L194" s="4"/>
-      <c r="M194" s="5"/>
-      <c r="N194" s="6"/>
-      <c r="O194" s="6"/>
-      <c r="P194" s="7"/>
-      <c r="Q194" s="8"/>
-      <c r="R194" s="8"/>
-      <c r="S194" s="8"/>
-      <c r="T194" s="9"/>
-      <c r="U194" s="9"/>
-      <c r="V194" s="9"/>
-      <c r="W194" s="9"/>
-      <c r="X194" s="9"/>
-      <c r="Y194" s="9"/>
-      <c r="Z194" s="9"/>
-      <c r="AA194" s="9"/>
-      <c r="AB194" s="9"/>
-      <c r="AC194" s="9"/>
-      <c r="AD194" s="6"/>
-      <c r="AE194" s="6"/>
-      <c r="AF194" s="6"/>
-      <c r="AG194" s="6"/>
-      <c r="AH194" s="6"/>
-      <c r="AI194" s="6"/>
-      <c r="AJ194" s="6"/>
-      <c r="AK194" s="6"/>
-      <c r="AL194" s="6"/>
-      <c r="AM194" s="6"/>
-      <c r="AN194" s="9"/>
-      <c r="AO194" s="6"/>
+      <c r="M194" s="5">
+        <v>4152.6000000000004</v>
+      </c>
+      <c r="N194" s="6">
+        <v>51</v>
+      </c>
+      <c r="O194" s="6">
+        <v>36</v>
+      </c>
+      <c r="P194" s="7">
+        <v>9.0368596153846159</v>
+      </c>
+      <c r="Q194" s="8">
+        <v>25.559596969696969</v>
+      </c>
+      <c r="R194" s="8">
+        <v>12.781183870967743</v>
+      </c>
+      <c r="S194" s="8">
+        <v>7</v>
+      </c>
+      <c r="T194" s="9">
+        <v>0.15151515151515152</v>
+      </c>
+      <c r="U194" s="9">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="V194" s="9">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="W194" s="9">
+        <v>0</v>
+      </c>
+      <c r="X194" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y194" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA194" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="AB194" s="9">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="AC194" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AD194" s="6">
+        <v>18</v>
+      </c>
+      <c r="AE194" s="6">
+        <v>17</v>
+      </c>
+      <c r="AF194" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK194" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL194" s="6">
+        <v>11</v>
+      </c>
+      <c r="AM194" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO194" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP194" s="4">
         <v>58</v>
       </c>
@@ -28562,7 +30360,7 @@
         <v>19947</v>
       </c>
       <c r="B197" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C197" s="4">
         <v>51</v>
@@ -28592,35 +30390,93 @@
         <v>58</v>
       </c>
       <c r="L197" s="4"/>
-      <c r="M197" s="5"/>
-      <c r="N197" s="6"/>
-      <c r="O197" s="6"/>
-      <c r="P197" s="7"/>
-      <c r="Q197" s="8"/>
-      <c r="R197" s="8"/>
-      <c r="S197" s="8"/>
-      <c r="T197" s="9"/>
-      <c r="U197" s="9"/>
-      <c r="V197" s="9"/>
-      <c r="W197" s="9"/>
-      <c r="X197" s="9"/>
-      <c r="Y197" s="9"/>
-      <c r="Z197" s="9"/>
-      <c r="AA197" s="9"/>
-      <c r="AB197" s="9"/>
-      <c r="AC197" s="9"/>
-      <c r="AD197" s="6"/>
-      <c r="AE197" s="6"/>
-      <c r="AF197" s="6"/>
-      <c r="AG197" s="6"/>
-      <c r="AH197" s="6"/>
-      <c r="AI197" s="6"/>
-      <c r="AJ197" s="6"/>
-      <c r="AK197" s="6"/>
-      <c r="AL197" s="6"/>
-      <c r="AM197" s="6"/>
-      <c r="AN197" s="9"/>
-      <c r="AO197" s="6"/>
+      <c r="M197" s="5">
+        <v>15275.08</v>
+      </c>
+      <c r="N197" s="6">
+        <v>144</v>
+      </c>
+      <c r="O197" s="6">
+        <v>89</v>
+      </c>
+      <c r="P197" s="7">
+        <v>2.9901893617021273</v>
+      </c>
+      <c r="Q197" s="8">
+        <v>16.966292134831459</v>
+      </c>
+      <c r="R197" s="8">
+        <v>7.2000000000000002</v>
+      </c>
+      <c r="S197" s="8">
+        <v>7</v>
+      </c>
+      <c r="T197" s="9">
+        <v>0.33707865168539325</v>
+      </c>
+      <c r="U197" s="9">
+        <v>0.06741573033707865</v>
+      </c>
+      <c r="V197" s="9">
+        <v>0</v>
+      </c>
+      <c r="W197" s="9">
+        <v>0</v>
+      </c>
+      <c r="X197" s="9">
+        <v>0.033707865168539325</v>
+      </c>
+      <c r="Y197" s="9">
+        <v>0.011235955056179775</v>
+      </c>
+      <c r="Z197" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA197" s="9">
+        <v>0.011235955056179775</v>
+      </c>
+      <c r="AB197" s="9">
+        <v>0.056179775280898875</v>
+      </c>
+      <c r="AC197" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD197" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE197" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF197" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG197" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH197" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI197" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ197" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK197" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL197" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM197" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN197" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO197" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP197" s="4">
         <v>58</v>
       </c>
@@ -28818,7 +30674,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>51</v>
@@ -28848,35 +30704,93 @@
         <v>58</v>
       </c>
       <c r="L199" s="4"/>
-      <c r="M199" s="5"/>
-      <c r="N199" s="6"/>
-      <c r="O199" s="6"/>
-      <c r="P199" s="7"/>
-      <c r="Q199" s="8"/>
-      <c r="R199" s="8"/>
-      <c r="S199" s="8"/>
-      <c r="T199" s="9"/>
-      <c r="U199" s="9"/>
-      <c r="V199" s="9"/>
-      <c r="W199" s="9"/>
-      <c r="X199" s="9"/>
-      <c r="Y199" s="9"/>
-      <c r="Z199" s="9"/>
-      <c r="AA199" s="9"/>
-      <c r="AB199" s="9"/>
-      <c r="AC199" s="9"/>
-      <c r="AD199" s="6"/>
-      <c r="AE199" s="6"/>
-      <c r="AF199" s="6"/>
-      <c r="AG199" s="6"/>
-      <c r="AH199" s="6"/>
-      <c r="AI199" s="6"/>
-      <c r="AJ199" s="6"/>
-      <c r="AK199" s="6"/>
-      <c r="AL199" s="6"/>
-      <c r="AM199" s="6"/>
-      <c r="AN199" s="9"/>
-      <c r="AO199" s="6"/>
+      <c r="M199" s="5">
+        <v>8075.3100000000004</v>
+      </c>
+      <c r="N199" s="6">
+        <v>85</v>
+      </c>
+      <c r="O199" s="6">
+        <v>47</v>
+      </c>
+      <c r="P199" s="7">
+        <v>8.0562253012048188</v>
+      </c>
+      <c r="Q199" s="8">
+        <v>42.432608695652178</v>
+      </c>
+      <c r="R199" s="8">
+        <v>27.160869565217393</v>
+      </c>
+      <c r="S199" s="8">
+        <v>7</v>
+      </c>
+      <c r="T199" s="9">
+        <v>0.065217391304347824</v>
+      </c>
+      <c r="U199" s="9">
+        <v>0.34042553191489361</v>
+      </c>
+      <c r="V199" s="9">
+        <v>0</v>
+      </c>
+      <c r="W199" s="9">
+        <v>0.021276595743999999</v>
+      </c>
+      <c r="X199" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y199" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD199" s="6">
+        <v>15</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG199" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN199" s="9">
+        <v>0.31914893617021278</v>
+      </c>
+      <c r="AO199" s="6">
+        <v>15</v>
+      </c>
       <c t="s" r="AP199" s="4">
         <v>58</v>
       </c>
@@ -28917,7 +30831,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>51</v>
@@ -28947,35 +30861,93 @@
         <v>58</v>
       </c>
       <c r="L200" s="4"/>
-      <c r="M200" s="5"/>
-      <c r="N200" s="6"/>
-      <c r="O200" s="6"/>
-      <c r="P200" s="7"/>
-      <c r="Q200" s="8"/>
-      <c r="R200" s="8"/>
-      <c r="S200" s="8"/>
-      <c r="T200" s="9"/>
-      <c r="U200" s="9"/>
-      <c r="V200" s="9"/>
-      <c r="W200" s="9"/>
-      <c r="X200" s="9"/>
-      <c r="Y200" s="9"/>
-      <c r="Z200" s="9"/>
-      <c r="AA200" s="9"/>
-      <c r="AB200" s="9"/>
-      <c r="AC200" s="9"/>
-      <c r="AD200" s="6"/>
-      <c r="AE200" s="6"/>
-      <c r="AF200" s="6"/>
-      <c r="AG200" s="6"/>
-      <c r="AH200" s="6"/>
-      <c r="AI200" s="6"/>
-      <c r="AJ200" s="6"/>
-      <c r="AK200" s="6"/>
-      <c r="AL200" s="6"/>
-      <c r="AM200" s="6"/>
-      <c r="AN200" s="9"/>
-      <c r="AO200" s="6"/>
+      <c r="M200" s="5">
+        <v>2923.0799999999999</v>
+      </c>
+      <c r="N200" s="6">
+        <v>39</v>
+      </c>
+      <c r="O200" s="6">
+        <v>12</v>
+      </c>
+      <c r="P200" s="7">
+        <v>9.8286333333333342</v>
+      </c>
+      <c r="Q200" s="8">
+        <v>22.002775</v>
+      </c>
+      <c r="R200" s="8">
+        <v>5.7819416666666674</v>
+      </c>
+      <c r="S200" s="8">
+        <v>7</v>
+      </c>
+      <c r="T200" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U200" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="V200" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="W200" s="9">
+        <v>0</v>
+      </c>
+      <c r="X200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC200" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AD200" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM200" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO200" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP200" s="4">
         <v>58</v>
       </c>
@@ -29685,7 +31657,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>51</v>
@@ -29715,35 +31687,93 @@
         <v>58</v>
       </c>
       <c r="L206" s="4"/>
-      <c r="M206" s="5"/>
-      <c r="N206" s="6"/>
-      <c r="O206" s="6"/>
-      <c r="P206" s="7"/>
-      <c r="Q206" s="8"/>
-      <c r="R206" s="8"/>
-      <c r="S206" s="8"/>
-      <c r="T206" s="9"/>
-      <c r="U206" s="9"/>
-      <c r="V206" s="9"/>
-      <c r="W206" s="9"/>
-      <c r="X206" s="9"/>
-      <c r="Y206" s="9"/>
-      <c r="Z206" s="9"/>
-      <c r="AA206" s="9"/>
-      <c r="AB206" s="9"/>
-      <c r="AC206" s="9"/>
-      <c r="AD206" s="6"/>
-      <c r="AE206" s="6"/>
-      <c r="AF206" s="6"/>
-      <c r="AG206" s="6"/>
-      <c r="AH206" s="6"/>
-      <c r="AI206" s="6"/>
-      <c r="AJ206" s="6"/>
-      <c r="AK206" s="6"/>
-      <c r="AL206" s="6"/>
-      <c r="AM206" s="6"/>
-      <c r="AN206" s="9"/>
-      <c r="AO206" s="6"/>
+      <c r="M206" s="5">
+        <v>4441.04</v>
+      </c>
+      <c r="N206" s="6">
+        <v>44</v>
+      </c>
+      <c r="O206" s="6">
+        <v>27</v>
+      </c>
+      <c r="P206" s="7">
+        <v>14.660984090909091</v>
+      </c>
+      <c r="Q206" s="8">
+        <v>35.876544444444441</v>
+      </c>
+      <c r="R206" s="8">
+        <v>13.117899999999999</v>
+      </c>
+      <c r="S206" s="8">
+        <v>7</v>
+      </c>
+      <c r="T206" s="9">
+        <v>0</v>
+      </c>
+      <c r="U206" s="9">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="V206" s="9">
+        <v>0</v>
+      </c>
+      <c r="W206" s="9">
+        <v>0</v>
+      </c>
+      <c r="X206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA206" s="9">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="AB206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD206" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK206" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO206" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP206" s="4">
         <v>58</v>
       </c>
